--- a/Baba Balance material list_24_04_2026.xlsx
+++ b/Baba Balance material list_24_04_2026.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/782417d650b27398/Desktop/Sharad Akshay/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Amalgam_Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F72DFC78-08ED-46ED-9565-CB57361DC9F6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{93EE9350-8A36-417A-9204-D3CC504F52AB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="243" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="243" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Baba balance material" sheetId="3" r:id="rId1"/>
@@ -681,7 +681,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -717,6 +716,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -999,19 +1001,19 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A2:AQ96"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="3.33203125" customWidth="1"/>
-    <col min="2" max="2" width="6.5546875" style="2" customWidth="1"/>
-    <col min="3" max="3" width="41.109375" customWidth="1"/>
-    <col min="4" max="4" width="15.109375" customWidth="1"/>
-    <col min="5" max="5" width="16.33203125" style="2" hidden="1" customWidth="1"/>
-    <col min="6" max="6" width="15.6640625" style="2" hidden="1" customWidth="1"/>
-    <col min="7" max="7" width="18.44140625" style="2" customWidth="1"/>
-    <col min="8" max="8" width="15.5546875" customWidth="1"/>
+    <col min="1" max="1" width="3.28515625" customWidth="1"/>
+    <col min="2" max="2" width="6.5703125" style="2" customWidth="1"/>
+    <col min="3" max="3" width="41.140625" customWidth="1"/>
+    <col min="4" max="4" width="15.140625" customWidth="1"/>
+    <col min="5" max="5" width="16.28515625" style="2" hidden="1" customWidth="1"/>
+    <col min="6" max="6" width="15.7109375" style="2" hidden="1" customWidth="1"/>
+    <col min="7" max="7" width="18.42578125" style="2" customWidth="1"/>
+    <col min="8" max="8" width="15.5703125" style="2" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="2:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="E2" s="5">
         <v>46022</v>
       </c>
@@ -1019,22 +1021,22 @@
         <v>46175</v>
       </c>
     </row>
-    <row r="3" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B3" s="34" t="s">
+    <row r="3" spans="2:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B3" s="33" t="s">
         <v>91</v>
       </c>
-      <c r="C3" s="35"/>
-      <c r="D3" s="35"/>
-      <c r="E3" s="36"/>
+      <c r="C3" s="34"/>
+      <c r="D3" s="34"/>
+      <c r="E3" s="35"/>
       <c r="F3" s="24"/>
       <c r="G3" s="24"/>
-      <c r="H3" s="25"/>
-    </row>
-    <row r="4" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="H3" s="37"/>
+    </row>
+    <row r="4" spans="2:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="F4" s="17"/>
       <c r="G4" s="17"/>
     </row>
-    <row r="5" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="2:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B5" s="10" t="s">
         <v>1</v>
       </c>
@@ -1053,11 +1055,11 @@
       <c r="G5" s="10" t="s">
         <v>93</v>
       </c>
-      <c r="H5" s="26" t="s">
+      <c r="H5" s="25" t="s">
         <v>92</v>
       </c>
     </row>
-    <row r="6" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="6" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B6" s="13">
         <v>1</v>
       </c>
@@ -1074,9 +1076,9 @@
       <c r="G6" s="1">
         <v>0</v>
       </c>
-      <c r="H6" s="3"/>
-    </row>
-    <row r="7" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="H6" s="1"/>
+    </row>
+    <row r="7" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B7" s="1">
         <v>2</v>
       </c>
@@ -1093,9 +1095,9 @@
       <c r="G7" s="1">
         <v>2</v>
       </c>
-      <c r="H7" s="3"/>
-    </row>
-    <row r="8" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="H7" s="1"/>
+    </row>
+    <row r="8" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B8" s="1">
         <v>3</v>
       </c>
@@ -1112,9 +1114,9 @@
       <c r="G8" s="1" t="s">
         <v>121</v>
       </c>
-      <c r="H8" s="3"/>
-    </row>
-    <row r="9" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="H8" s="1"/>
+    </row>
+    <row r="9" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B9" s="1">
         <v>4</v>
       </c>
@@ -1131,9 +1133,9 @@
       <c r="G9" s="1">
         <v>2</v>
       </c>
-      <c r="H9" s="3"/>
-    </row>
-    <row r="10" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="H9" s="1"/>
+    </row>
+    <row r="10" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B10" s="1">
         <v>5</v>
       </c>
@@ -1150,9 +1152,9 @@
       <c r="G10" s="1">
         <v>116</v>
       </c>
-      <c r="H10" s="3"/>
-    </row>
-    <row r="11" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="H10" s="1"/>
+    </row>
+    <row r="11" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B11" s="1">
         <v>6</v>
       </c>
@@ -1169,9 +1171,9 @@
       <c r="G11" s="1">
         <v>53</v>
       </c>
-      <c r="H11" s="3"/>
-    </row>
-    <row r="12" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="H11" s="1"/>
+    </row>
+    <row r="12" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B12" s="1">
         <v>7</v>
       </c>
@@ -1188,9 +1190,9 @@
       <c r="G12" s="1">
         <v>7</v>
       </c>
-      <c r="H12" s="3"/>
-    </row>
-    <row r="13" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="H12" s="1"/>
+    </row>
+    <row r="13" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B13" s="1">
         <v>8</v>
       </c>
@@ -1207,9 +1209,9 @@
       <c r="G13" s="1">
         <v>4</v>
       </c>
-      <c r="H13" s="3"/>
-    </row>
-    <row r="14" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="H13" s="1"/>
+    </row>
+    <row r="14" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B14" s="1">
         <v>9</v>
       </c>
@@ -1226,9 +1228,9 @@
       <c r="G14" s="1">
         <v>18</v>
       </c>
-      <c r="H14" s="3"/>
-    </row>
-    <row r="15" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="H14" s="1"/>
+    </row>
+    <row r="15" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B15" s="1">
         <v>10</v>
       </c>
@@ -1245,9 +1247,9 @@
       <c r="G15" s="1">
         <v>123</v>
       </c>
-      <c r="H15" s="3"/>
-    </row>
-    <row r="16" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="H15" s="1"/>
+    </row>
+    <row r="16" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B16" s="1">
         <v>11</v>
       </c>
@@ -1264,9 +1266,9 @@
       <c r="G16" s="1">
         <v>73</v>
       </c>
-      <c r="H16" s="3"/>
-    </row>
-    <row r="17" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="H16" s="1"/>
+    </row>
+    <row r="17" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B17" s="1">
         <v>12</v>
       </c>
@@ -1283,9 +1285,9 @@
       <c r="G17" s="1">
         <v>0</v>
       </c>
-      <c r="H17" s="3"/>
-    </row>
-    <row r="18" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="H17" s="1"/>
+    </row>
+    <row r="18" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B18" s="1">
         <v>13</v>
       </c>
@@ -1302,9 +1304,9 @@
       <c r="G18" s="1">
         <v>2</v>
       </c>
-      <c r="H18" s="3"/>
-    </row>
-    <row r="19" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="H18" s="1"/>
+    </row>
+    <row r="19" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B19" s="1">
         <v>14</v>
       </c>
@@ -1321,9 +1323,9 @@
       <c r="G19" s="1">
         <v>0</v>
       </c>
-      <c r="H19" s="3"/>
-    </row>
-    <row r="20" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="H19" s="1"/>
+    </row>
+    <row r="20" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B20" s="1">
         <v>15</v>
       </c>
@@ -1340,9 +1342,9 @@
       <c r="G20" s="1">
         <v>0</v>
       </c>
-      <c r="H20" s="3"/>
-    </row>
-    <row r="21" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="H20" s="1"/>
+    </row>
+    <row r="21" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B21" s="1">
         <v>16</v>
       </c>
@@ -1359,9 +1361,9 @@
       <c r="G21" s="1">
         <v>5</v>
       </c>
-      <c r="H21" s="3"/>
-    </row>
-    <row r="22" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="H21" s="1"/>
+    </row>
+    <row r="22" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B22" s="1">
         <v>17</v>
       </c>
@@ -1378,9 +1380,9 @@
       <c r="G22" s="1">
         <v>5</v>
       </c>
-      <c r="H22" s="3"/>
-    </row>
-    <row r="23" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="H22" s="1"/>
+    </row>
+    <row r="23" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B23" s="1">
         <v>18</v>
       </c>
@@ -1397,9 +1399,9 @@
       <c r="G23" s="1">
         <v>2</v>
       </c>
-      <c r="H23" s="3"/>
-    </row>
-    <row r="24" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="H23" s="1"/>
+    </row>
+    <row r="24" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B24" s="1">
         <v>19</v>
       </c>
@@ -1416,9 +1418,9 @@
       <c r="G24" s="1">
         <v>6</v>
       </c>
-      <c r="H24" s="3"/>
-    </row>
-    <row r="25" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="H24" s="1"/>
+    </row>
+    <row r="25" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B25" s="1">
         <v>20</v>
       </c>
@@ -1435,9 +1437,9 @@
       <c r="G25" s="1">
         <v>0</v>
       </c>
-      <c r="H25" s="3"/>
-    </row>
-    <row r="26" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="H25" s="1"/>
+    </row>
+    <row r="26" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B26" s="1">
         <v>21</v>
       </c>
@@ -1454,9 +1456,9 @@
       <c r="G26" s="1">
         <v>15</v>
       </c>
-      <c r="H26" s="3"/>
-    </row>
-    <row r="27" spans="2:8" s="9" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="H26" s="1"/>
+    </row>
+    <row r="27" spans="2:8" s="9" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B27" s="1">
         <v>22</v>
       </c>
@@ -1473,9 +1475,9 @@
       <c r="G27" s="15" t="s">
         <v>103</v>
       </c>
-      <c r="H27" s="7"/>
-    </row>
-    <row r="28" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="H27" s="15"/>
+    </row>
+    <row r="28" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B28" s="1">
         <v>23</v>
       </c>
@@ -1492,9 +1494,9 @@
       <c r="G28" s="1">
         <v>1</v>
       </c>
-      <c r="H28" s="3"/>
-    </row>
-    <row r="29" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="H28" s="1"/>
+    </row>
+    <row r="29" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B29" s="1">
         <v>24</v>
       </c>
@@ -1511,9 +1513,9 @@
       <c r="G29" s="1">
         <v>6</v>
       </c>
-      <c r="H29" s="3"/>
-    </row>
-    <row r="30" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="H29" s="1"/>
+    </row>
+    <row r="30" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B30" s="1">
         <v>25</v>
       </c>
@@ -1530,9 +1532,9 @@
       <c r="G30" s="1">
         <v>1</v>
       </c>
-      <c r="H30" s="3"/>
-    </row>
-    <row r="31" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="H30" s="1"/>
+    </row>
+    <row r="31" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B31" s="1">
         <v>26</v>
       </c>
@@ -1549,9 +1551,9 @@
       <c r="G31" s="1">
         <v>4</v>
       </c>
-      <c r="H31" s="3"/>
-    </row>
-    <row r="32" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="H31" s="1"/>
+    </row>
+    <row r="32" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B32" s="1">
         <v>27</v>
       </c>
@@ -1568,9 +1570,9 @@
       <c r="G32" s="1">
         <v>0</v>
       </c>
-      <c r="H32" s="3"/>
-    </row>
-    <row r="33" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="H32" s="1"/>
+    </row>
+    <row r="33" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B33" s="1">
         <v>28</v>
       </c>
@@ -1587,9 +1589,9 @@
       <c r="G33" s="1" t="s">
         <v>100</v>
       </c>
-      <c r="H33" s="3"/>
-    </row>
-    <row r="34" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="H33" s="1"/>
+    </row>
+    <row r="34" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B34" s="1">
         <v>29</v>
       </c>
@@ -1606,9 +1608,9 @@
       <c r="G34" s="1">
         <v>5</v>
       </c>
-      <c r="H34" s="3"/>
-    </row>
-    <row r="35" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="H34" s="1"/>
+    </row>
+    <row r="35" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B35" s="1">
         <v>30</v>
       </c>
@@ -1625,9 +1627,9 @@
       <c r="G35" s="1">
         <v>4</v>
       </c>
-      <c r="H35" s="3"/>
-    </row>
-    <row r="36" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="H35" s="1"/>
+    </row>
+    <row r="36" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B36" s="1">
         <v>31</v>
       </c>
@@ -1644,12 +1646,12 @@
       <c r="G36" s="1">
         <v>1</v>
       </c>
-      <c r="H36" s="3"/>
+      <c r="H36" s="1"/>
       <c r="I36" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="37" spans="2:9" x14ac:dyDescent="0.3">
+    <row r="37" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B37" s="1">
         <v>32</v>
       </c>
@@ -1666,9 +1668,9 @@
       <c r="G37" s="1">
         <v>2</v>
       </c>
-      <c r="H37" s="3"/>
-    </row>
-    <row r="38" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="H37" s="1"/>
+    </row>
+    <row r="38" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B38" s="1">
         <v>33</v>
       </c>
@@ -1685,9 +1687,9 @@
       <c r="G38" s="1">
         <v>6</v>
       </c>
-      <c r="H38" s="3"/>
-    </row>
-    <row r="39" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="H38" s="1"/>
+    </row>
+    <row r="39" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B39" s="1">
         <v>34</v>
       </c>
@@ -1704,9 +1706,9 @@
       <c r="G39" s="1">
         <v>0</v>
       </c>
-      <c r="H39" s="3"/>
-    </row>
-    <row r="40" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="H39" s="1"/>
+    </row>
+    <row r="40" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B40" s="1">
         <v>35</v>
       </c>
@@ -1723,9 +1725,9 @@
       <c r="G40" s="1">
         <v>0</v>
       </c>
-      <c r="H40" s="3"/>
-    </row>
-    <row r="41" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="H40" s="1"/>
+    </row>
+    <row r="41" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B41" s="1">
         <v>36</v>
       </c>
@@ -1742,9 +1744,9 @@
       <c r="G41" s="1">
         <v>13</v>
       </c>
-      <c r="H41" s="3"/>
-    </row>
-    <row r="42" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="H41" s="1"/>
+    </row>
+    <row r="42" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B42" s="1">
         <v>37</v>
       </c>
@@ -1761,9 +1763,9 @@
       <c r="G42" s="1">
         <v>2</v>
       </c>
-      <c r="H42" s="3"/>
-    </row>
-    <row r="43" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="H42" s="1"/>
+    </row>
+    <row r="43" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B43" s="1">
         <v>38</v>
       </c>
@@ -1780,9 +1782,9 @@
       <c r="G43" s="1">
         <v>2</v>
       </c>
-      <c r="H43" s="3"/>
-    </row>
-    <row r="44" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="H43" s="1"/>
+    </row>
+    <row r="44" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B44" s="1">
         <v>39</v>
       </c>
@@ -1799,9 +1801,9 @@
       <c r="G44" s="1">
         <v>1</v>
       </c>
-      <c r="H44" s="3"/>
-    </row>
-    <row r="45" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="H44" s="1"/>
+    </row>
+    <row r="45" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B45" s="1">
         <v>40</v>
       </c>
@@ -1818,9 +1820,9 @@
       <c r="G45" s="1">
         <v>7</v>
       </c>
-      <c r="H45" s="3"/>
-    </row>
-    <row r="46" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="H45" s="1"/>
+    </row>
+    <row r="46" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B46" s="1">
         <v>41</v>
       </c>
@@ -1837,13 +1839,13 @@
       <c r="G46" s="1">
         <v>24</v>
       </c>
-      <c r="H46" s="3"/>
-    </row>
-    <row r="47" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B47" s="31">
+      <c r="H46" s="1"/>
+    </row>
+    <row r="47" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B47" s="30">
         <v>42</v>
       </c>
-      <c r="C47" s="28" t="s">
+      <c r="C47" s="27" t="s">
         <v>82</v>
       </c>
       <c r="D47" s="3" t="s">
@@ -1858,11 +1860,11 @@
       <c r="G47" s="1">
         <v>9</v>
       </c>
-      <c r="H47" s="3"/>
-    </row>
-    <row r="48" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B48" s="32"/>
-      <c r="C48" s="29"/>
+      <c r="H47" s="1"/>
+    </row>
+    <row r="48" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B48" s="31"/>
+      <c r="C48" s="28"/>
       <c r="D48" s="3" t="s">
         <v>78</v>
       </c>
@@ -1875,11 +1877,11 @@
       <c r="G48" s="1">
         <v>9</v>
       </c>
-      <c r="H48" s="3"/>
-    </row>
-    <row r="49" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B49" s="32"/>
-      <c r="C49" s="29"/>
+      <c r="H48" s="1"/>
+    </row>
+    <row r="49" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B49" s="31"/>
+      <c r="C49" s="28"/>
       <c r="D49" s="3" t="s">
         <v>79</v>
       </c>
@@ -1892,11 +1894,11 @@
       <c r="G49" s="1">
         <v>9</v>
       </c>
-      <c r="H49" s="3"/>
-    </row>
-    <row r="50" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B50" s="32"/>
-      <c r="C50" s="29"/>
+      <c r="H49" s="1"/>
+    </row>
+    <row r="50" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B50" s="31"/>
+      <c r="C50" s="28"/>
       <c r="D50" s="3" t="s">
         <v>76</v>
       </c>
@@ -1909,11 +1911,11 @@
       <c r="G50" s="1">
         <v>9</v>
       </c>
-      <c r="H50" s="3"/>
-    </row>
-    <row r="51" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B51" s="32"/>
-      <c r="C51" s="29"/>
+      <c r="H50" s="1"/>
+    </row>
+    <row r="51" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B51" s="31"/>
+      <c r="C51" s="28"/>
       <c r="D51" s="3" t="s">
         <v>80</v>
       </c>
@@ -1926,11 +1928,11 @@
       <c r="G51" s="1">
         <v>9</v>
       </c>
-      <c r="H51" s="3"/>
-    </row>
-    <row r="52" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B52" s="33"/>
-      <c r="C52" s="30"/>
+      <c r="H51" s="1"/>
+    </row>
+    <row r="52" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B52" s="32"/>
+      <c r="C52" s="29"/>
       <c r="D52" s="3" t="s">
         <v>81</v>
       </c>
@@ -1943,13 +1945,13 @@
       <c r="G52" s="1">
         <v>17</v>
       </c>
-      <c r="H52" s="3"/>
-    </row>
-    <row r="53" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B53" s="31">
+      <c r="H52" s="1"/>
+    </row>
+    <row r="53" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B53" s="30">
         <v>43</v>
       </c>
-      <c r="C53" s="28" t="s">
+      <c r="C53" s="27" t="s">
         <v>83</v>
       </c>
       <c r="D53" s="3" t="s">
@@ -1964,11 +1966,11 @@
       <c r="G53" s="1">
         <v>11</v>
       </c>
-      <c r="H53" s="3"/>
-    </row>
-    <row r="54" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B54" s="32"/>
-      <c r="C54" s="29"/>
+      <c r="H53" s="1"/>
+    </row>
+    <row r="54" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B54" s="31"/>
+      <c r="C54" s="28"/>
       <c r="D54" s="3" t="s">
         <v>85</v>
       </c>
@@ -1981,11 +1983,11 @@
       <c r="G54" s="1">
         <v>10</v>
       </c>
-      <c r="H54" s="3"/>
-    </row>
-    <row r="55" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B55" s="32"/>
-      <c r="C55" s="29"/>
+      <c r="H54" s="1"/>
+    </row>
+    <row r="55" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B55" s="31"/>
+      <c r="C55" s="28"/>
       <c r="D55" s="3" t="s">
         <v>86</v>
       </c>
@@ -1998,11 +2000,11 @@
       <c r="G55" s="1">
         <v>10</v>
       </c>
-      <c r="H55" s="3"/>
-    </row>
-    <row r="56" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B56" s="32"/>
-      <c r="C56" s="29"/>
+      <c r="H55" s="1"/>
+    </row>
+    <row r="56" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B56" s="31"/>
+      <c r="C56" s="28"/>
       <c r="D56" s="3" t="s">
         <v>87</v>
       </c>
@@ -2015,11 +2017,11 @@
       <c r="G56" s="1">
         <v>10</v>
       </c>
-      <c r="H56" s="3"/>
-    </row>
-    <row r="57" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B57" s="32"/>
-      <c r="C57" s="29"/>
+      <c r="H56" s="1"/>
+    </row>
+    <row r="57" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B57" s="31"/>
+      <c r="C57" s="28"/>
       <c r="D57" s="3" t="s">
         <v>88</v>
       </c>
@@ -2032,11 +2034,11 @@
       <c r="G57" s="1">
         <v>9</v>
       </c>
-      <c r="H57" s="3"/>
-    </row>
-    <row r="58" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B58" s="32"/>
-      <c r="C58" s="29"/>
+      <c r="H57" s="1"/>
+    </row>
+    <row r="58" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B58" s="31"/>
+      <c r="C58" s="28"/>
       <c r="D58" s="3" t="s">
         <v>89</v>
       </c>
@@ -2049,9 +2051,9 @@
       <c r="G58" s="1">
         <v>10</v>
       </c>
-      <c r="H58" s="3"/>
-    </row>
-    <row r="59" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="H58" s="1"/>
+    </row>
+    <row r="59" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B59" s="1">
         <v>44</v>
       </c>
@@ -2068,9 +2070,9 @@
       <c r="G59" s="1">
         <v>0</v>
       </c>
-      <c r="H59" s="3"/>
-    </row>
-    <row r="60" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="H59" s="1"/>
+    </row>
+    <row r="60" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B60" s="1">
         <v>45</v>
       </c>
@@ -2087,9 +2089,9 @@
       <c r="G60" s="1">
         <v>2</v>
       </c>
-      <c r="H60" s="3"/>
-    </row>
-    <row r="61" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="H60" s="1"/>
+    </row>
+    <row r="61" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B61" s="1">
         <v>46</v>
       </c>
@@ -2106,13 +2108,13 @@
       <c r="G61" s="1">
         <v>1</v>
       </c>
-      <c r="H61" s="3"/>
-    </row>
-    <row r="62" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B62" s="31">
+      <c r="H61" s="1"/>
+    </row>
+    <row r="62" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B62" s="30">
         <v>47</v>
       </c>
-      <c r="C62" s="28" t="s">
+      <c r="C62" s="27" t="s">
         <v>111</v>
       </c>
       <c r="D62" s="3" t="s">
@@ -2127,11 +2129,11 @@
       <c r="G62" s="1">
         <v>1</v>
       </c>
-      <c r="H62" s="3"/>
-    </row>
-    <row r="63" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B63" s="32"/>
-      <c r="C63" s="29"/>
+      <c r="H62" s="1"/>
+    </row>
+    <row r="63" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B63" s="31"/>
+      <c r="C63" s="28"/>
       <c r="D63" s="3" t="s">
         <v>117</v>
       </c>
@@ -2144,11 +2146,11 @@
       <c r="G63" s="1">
         <v>2</v>
       </c>
-      <c r="H63" s="3"/>
-    </row>
-    <row r="64" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B64" s="33"/>
-      <c r="C64" s="30"/>
+      <c r="H63" s="1"/>
+    </row>
+    <row r="64" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B64" s="32"/>
+      <c r="C64" s="29"/>
       <c r="D64" s="3" t="s">
         <v>52</v>
       </c>
@@ -2161,9 +2163,9 @@
       <c r="G64" s="1">
         <v>1</v>
       </c>
-      <c r="H64" s="3"/>
-    </row>
-    <row r="65" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="H64" s="1"/>
+    </row>
+    <row r="65" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B65" s="1">
         <v>48</v>
       </c>
@@ -2182,13 +2184,13 @@
       <c r="G65" s="1">
         <v>2</v>
       </c>
-      <c r="H65" s="3"/>
-    </row>
-    <row r="66" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B66" s="27">
+      <c r="H65" s="1"/>
+    </row>
+    <row r="66" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B66" s="26">
         <v>49</v>
       </c>
-      <c r="C66" s="37" t="s">
+      <c r="C66" s="36" t="s">
         <v>42</v>
       </c>
       <c r="D66" s="3" t="s">
@@ -2203,11 +2205,11 @@
       <c r="G66" s="1">
         <v>0</v>
       </c>
-      <c r="H66" s="3"/>
-    </row>
-    <row r="67" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B67" s="27"/>
-      <c r="C67" s="37"/>
+      <c r="H66" s="1"/>
+    </row>
+    <row r="67" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B67" s="26"/>
+      <c r="C67" s="36"/>
       <c r="D67" s="3" t="s">
         <v>44</v>
       </c>
@@ -2220,11 +2222,11 @@
       <c r="G67" s="1">
         <v>0</v>
       </c>
-      <c r="H67" s="3"/>
-    </row>
-    <row r="68" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B68" s="27"/>
-      <c r="C68" s="37"/>
+      <c r="H67" s="1"/>
+    </row>
+    <row r="68" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B68" s="26"/>
+      <c r="C68" s="36"/>
       <c r="D68" s="3" t="s">
         <v>46</v>
       </c>
@@ -2237,11 +2239,11 @@
       <c r="G68" s="1">
         <v>0</v>
       </c>
-      <c r="H68" s="3"/>
-    </row>
-    <row r="69" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B69" s="27"/>
-      <c r="C69" s="37"/>
+      <c r="H68" s="1"/>
+    </row>
+    <row r="69" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B69" s="26"/>
+      <c r="C69" s="36"/>
       <c r="D69" s="3" t="s">
         <v>112</v>
       </c>
@@ -2254,11 +2256,11 @@
       <c r="G69" s="1">
         <v>2</v>
       </c>
-      <c r="H69" s="3"/>
-    </row>
-    <row r="70" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B70" s="27"/>
-      <c r="C70" s="37"/>
+      <c r="H69" s="1"/>
+    </row>
+    <row r="70" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B70" s="26"/>
+      <c r="C70" s="36"/>
       <c r="D70" s="3" t="s">
         <v>45</v>
       </c>
@@ -2271,13 +2273,13 @@
       <c r="G70" s="1">
         <v>3</v>
       </c>
-      <c r="H70" s="3"/>
-    </row>
-    <row r="71" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B71" s="27">
+      <c r="H70" s="1"/>
+    </row>
+    <row r="71" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B71" s="26">
         <v>50</v>
       </c>
-      <c r="C71" s="37" t="s">
+      <c r="C71" s="36" t="s">
         <v>47</v>
       </c>
       <c r="D71" s="3" t="s">
@@ -2292,11 +2294,11 @@
       <c r="G71" s="1">
         <v>4</v>
       </c>
-      <c r="H71" s="3"/>
-    </row>
-    <row r="72" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B72" s="27"/>
-      <c r="C72" s="37"/>
+      <c r="H71" s="1"/>
+    </row>
+    <row r="72" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B72" s="26"/>
+      <c r="C72" s="36"/>
       <c r="D72" s="3" t="s">
         <v>49</v>
       </c>
@@ -2309,11 +2311,11 @@
       <c r="G72" s="16" t="s">
         <v>124</v>
       </c>
-      <c r="H72" s="3"/>
-    </row>
-    <row r="73" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B73" s="27"/>
-      <c r="C73" s="37"/>
+      <c r="H72" s="1"/>
+    </row>
+    <row r="73" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B73" s="26"/>
+      <c r="C73" s="36"/>
       <c r="D73" s="3" t="s">
         <v>90</v>
       </c>
@@ -2326,11 +2328,11 @@
       <c r="G73" s="1">
         <v>1</v>
       </c>
-      <c r="H73" s="3"/>
-    </row>
-    <row r="74" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B74" s="27"/>
-      <c r="C74" s="37"/>
+      <c r="H73" s="1"/>
+    </row>
+    <row r="74" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B74" s="26"/>
+      <c r="C74" s="36"/>
       <c r="D74" s="3" t="s">
         <v>114</v>
       </c>
@@ -2343,11 +2345,11 @@
       <c r="G74" s="1" t="s">
         <v>129</v>
       </c>
-      <c r="H74" s="3"/>
-    </row>
-    <row r="75" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B75" s="27"/>
-      <c r="C75" s="37"/>
+      <c r="H74" s="1"/>
+    </row>
+    <row r="75" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B75" s="26"/>
+      <c r="C75" s="36"/>
       <c r="D75" s="3" t="s">
         <v>115</v>
       </c>
@@ -2360,13 +2362,13 @@
       <c r="G75" s="1">
         <v>2</v>
       </c>
-      <c r="H75" s="3"/>
-    </row>
-    <row r="76" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B76" s="31">
+      <c r="H75" s="1"/>
+    </row>
+    <row r="76" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B76" s="30">
         <v>51</v>
       </c>
-      <c r="C76" s="28" t="s">
+      <c r="C76" s="27" t="s">
         <v>50</v>
       </c>
       <c r="D76" s="3" t="s">
@@ -2381,11 +2383,11 @@
       <c r="G76" s="1">
         <v>1</v>
       </c>
-      <c r="H76" s="3"/>
-    </row>
-    <row r="77" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B77" s="32"/>
-      <c r="C77" s="29"/>
+      <c r="H76" s="1"/>
+    </row>
+    <row r="77" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B77" s="31"/>
+      <c r="C77" s="28"/>
       <c r="D77" s="3" t="s">
         <v>52</v>
       </c>
@@ -2398,11 +2400,11 @@
       <c r="G77" s="1">
         <v>3</v>
       </c>
-      <c r="H77" s="3"/>
-    </row>
-    <row r="78" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B78" s="33"/>
-      <c r="C78" s="30"/>
+      <c r="H77" s="1"/>
+    </row>
+    <row r="78" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B78" s="32"/>
+      <c r="C78" s="29"/>
       <c r="D78" s="3" t="s">
         <v>112</v>
       </c>
@@ -2415,13 +2417,13 @@
       <c r="G78" s="1" t="s">
         <v>130</v>
       </c>
-      <c r="H78" s="3"/>
-    </row>
-    <row r="79" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B79" s="31">
+      <c r="H78" s="1"/>
+    </row>
+    <row r="79" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B79" s="30">
         <v>52</v>
       </c>
-      <c r="C79" s="28" t="s">
+      <c r="C79" s="27" t="s">
         <v>53</v>
       </c>
       <c r="D79" s="3" t="s">
@@ -2436,11 +2438,11 @@
       <c r="G79" s="1">
         <v>1</v>
       </c>
-      <c r="H79" s="3"/>
-    </row>
-    <row r="80" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B80" s="32"/>
-      <c r="C80" s="29"/>
+      <c r="H79" s="1"/>
+    </row>
+    <row r="80" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B80" s="31"/>
+      <c r="C80" s="28"/>
       <c r="D80" s="3" t="s">
         <v>51</v>
       </c>
@@ -2453,11 +2455,11 @@
       <c r="G80" s="1">
         <v>1</v>
       </c>
-      <c r="H80" s="3"/>
-    </row>
-    <row r="81" spans="1:43" x14ac:dyDescent="0.3">
-      <c r="B81" s="32"/>
-      <c r="C81" s="29"/>
+      <c r="H80" s="1"/>
+    </row>
+    <row r="81" spans="1:43" x14ac:dyDescent="0.25">
+      <c r="B81" s="31"/>
+      <c r="C81" s="28"/>
       <c r="D81" s="3" t="s">
         <v>122</v>
       </c>
@@ -2470,11 +2472,11 @@
       <c r="G81" s="1">
         <v>5</v>
       </c>
-      <c r="H81" s="3"/>
-    </row>
-    <row r="82" spans="1:43" x14ac:dyDescent="0.3">
-      <c r="B82" s="32"/>
-      <c r="C82" s="29"/>
+      <c r="H81" s="1"/>
+    </row>
+    <row r="82" spans="1:43" x14ac:dyDescent="0.25">
+      <c r="B82" s="31"/>
+      <c r="C82" s="28"/>
       <c r="D82" s="3" t="s">
         <v>55</v>
       </c>
@@ -2487,9 +2489,9 @@
       <c r="G82" s="1">
         <v>2</v>
       </c>
-      <c r="H82" s="3"/>
-    </row>
-    <row r="83" spans="1:43" x14ac:dyDescent="0.3">
+      <c r="H82" s="1"/>
+    </row>
+    <row r="83" spans="1:43" x14ac:dyDescent="0.25">
       <c r="B83" s="1">
         <v>53</v>
       </c>
@@ -2506,9 +2508,9 @@
       <c r="G83" s="1">
         <v>11</v>
       </c>
-      <c r="H83" s="3"/>
-    </row>
-    <row r="84" spans="1:43" x14ac:dyDescent="0.3">
+      <c r="H83" s="1"/>
+    </row>
+    <row r="84" spans="1:43" x14ac:dyDescent="0.25">
       <c r="B84" s="1">
         <v>54</v>
       </c>
@@ -2525,9 +2527,9 @@
       <c r="G84" s="1">
         <v>5</v>
       </c>
-      <c r="H84" s="3"/>
-    </row>
-    <row r="85" spans="1:43" x14ac:dyDescent="0.3">
+      <c r="H84" s="1"/>
+    </row>
+    <row r="85" spans="1:43" x14ac:dyDescent="0.25">
       <c r="B85" s="1">
         <v>55</v>
       </c>
@@ -2544,9 +2546,9 @@
       <c r="G85" s="16" t="s">
         <v>123</v>
       </c>
-      <c r="H85" s="3"/>
-    </row>
-    <row r="86" spans="1:43" s="6" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="H85" s="1"/>
+    </row>
+    <row r="86" spans="1:43" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A86"/>
       <c r="B86" s="1">
         <v>56</v>
@@ -2564,7 +2566,7 @@
       <c r="G86" s="1">
         <v>5</v>
       </c>
-      <c r="H86" s="3"/>
+      <c r="H86" s="1"/>
       <c r="I86"/>
       <c r="J86"/>
       <c r="K86"/>
@@ -2601,7 +2603,7 @@
       <c r="AP86"/>
       <c r="AQ86"/>
     </row>
-    <row r="87" spans="1:43" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:43" x14ac:dyDescent="0.25">
       <c r="B87" s="1">
         <v>57</v>
       </c>
@@ -2618,9 +2620,9 @@
       <c r="G87" s="1">
         <v>16</v>
       </c>
-      <c r="H87" s="3"/>
-    </row>
-    <row r="88" spans="1:43" x14ac:dyDescent="0.3">
+      <c r="H87" s="1"/>
+    </row>
+    <row r="88" spans="1:43" x14ac:dyDescent="0.25">
       <c r="B88" s="1">
         <v>58</v>
       </c>
@@ -2637,9 +2639,9 @@
       <c r="G88" s="1">
         <v>13</v>
       </c>
-      <c r="H88" s="3"/>
-    </row>
-    <row r="89" spans="1:43" x14ac:dyDescent="0.3">
+      <c r="H88" s="1"/>
+    </row>
+    <row r="89" spans="1:43" x14ac:dyDescent="0.25">
       <c r="B89" s="1">
         <v>59</v>
       </c>
@@ -2656,9 +2658,9 @@
       <c r="G89" s="1">
         <v>4</v>
       </c>
-      <c r="H89" s="3"/>
-    </row>
-    <row r="90" spans="1:43" x14ac:dyDescent="0.3">
+      <c r="H89" s="1"/>
+    </row>
+    <row r="90" spans="1:43" x14ac:dyDescent="0.25">
       <c r="B90" s="1">
         <v>60</v>
       </c>
@@ -2675,9 +2677,9 @@
       <c r="G90" s="1">
         <v>12</v>
       </c>
-      <c r="H90" s="3"/>
-    </row>
-    <row r="91" spans="1:43" x14ac:dyDescent="0.3">
+      <c r="H90" s="1"/>
+    </row>
+    <row r="91" spans="1:43" x14ac:dyDescent="0.25">
       <c r="B91" s="1">
         <v>61</v>
       </c>
@@ -2694,9 +2696,9 @@
       <c r="G91" s="1">
         <v>29</v>
       </c>
-      <c r="H91" s="3"/>
-    </row>
-    <row r="92" spans="1:43" x14ac:dyDescent="0.3">
+      <c r="H91" s="1"/>
+    </row>
+    <row r="92" spans="1:43" x14ac:dyDescent="0.25">
       <c r="B92" s="1">
         <v>62</v>
       </c>
@@ -2715,9 +2717,9 @@
       <c r="G92" s="1">
         <v>25</v>
       </c>
-      <c r="H92" s="3"/>
-    </row>
-    <row r="93" spans="1:43" x14ac:dyDescent="0.3">
+      <c r="H92" s="1"/>
+    </row>
+    <row r="93" spans="1:43" x14ac:dyDescent="0.25">
       <c r="B93" s="1">
         <v>63</v>
       </c>
@@ -2730,9 +2732,11 @@
       <c r="G93" s="1">
         <v>395</v>
       </c>
-      <c r="H93" s="3"/>
-    </row>
-    <row r="94" spans="1:43" x14ac:dyDescent="0.3">
+      <c r="H93" s="1">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="94" spans="1:43" x14ac:dyDescent="0.25">
       <c r="B94" s="1">
         <v>64</v>
       </c>
@@ -2745,9 +2749,11 @@
       <c r="G94" s="1">
         <v>922</v>
       </c>
-      <c r="H94" s="3"/>
-    </row>
-    <row r="95" spans="1:43" x14ac:dyDescent="0.3">
+      <c r="H94" s="1">
+        <v>917</v>
+      </c>
+    </row>
+    <row r="95" spans="1:43" x14ac:dyDescent="0.25">
       <c r="B95" s="1">
         <v>65</v>
       </c>
@@ -2760,9 +2766,9 @@
       <c r="G95" s="1">
         <v>232</v>
       </c>
-      <c r="H95" s="3"/>
-    </row>
-    <row r="96" spans="1:43" x14ac:dyDescent="0.3">
+      <c r="H95" s="1"/>
+    </row>
+    <row r="96" spans="1:43" x14ac:dyDescent="0.25">
       <c r="B96" s="1">
         <v>66</v>
       </c>
@@ -2775,7 +2781,7 @@
       <c r="G96" s="1">
         <v>2000</v>
       </c>
-      <c r="H96" s="3"/>
+      <c r="H96" s="1"/>
     </row>
   </sheetData>
   <mergeCells count="15">

--- a/Baba Balance material list_24_04_2026.xlsx
+++ b/Baba Balance material list_24_04_2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Amalgam_Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{93EE9350-8A36-417A-9204-D3CC504F52AB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CB668635-F76C-4862-A367-A327247922C9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="243" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -684,6 +684,9 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -716,9 +719,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1020,17 +1020,20 @@
       <c r="G2" s="23">
         <v>46175</v>
       </c>
+      <c r="H2" s="17">
+        <v>46239</v>
+      </c>
     </row>
     <row r="3" spans="2:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B3" s="33" t="s">
+      <c r="B3" s="34" t="s">
         <v>91</v>
       </c>
-      <c r="C3" s="34"/>
-      <c r="D3" s="34"/>
-      <c r="E3" s="35"/>
+      <c r="C3" s="35"/>
+      <c r="D3" s="35"/>
+      <c r="E3" s="36"/>
       <c r="F3" s="24"/>
       <c r="G3" s="24"/>
-      <c r="H3" s="37"/>
+      <c r="H3" s="26"/>
     </row>
     <row r="4" spans="2:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="F4" s="17"/>
@@ -1304,7 +1307,9 @@
       <c r="G18" s="1">
         <v>2</v>
       </c>
-      <c r="H18" s="1"/>
+      <c r="H18" s="1">
+        <v>1</v>
+      </c>
     </row>
     <row r="19" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B19" s="1">
@@ -1380,7 +1385,9 @@
       <c r="G22" s="1">
         <v>5</v>
       </c>
-      <c r="H22" s="1"/>
+      <c r="H22" s="1">
+        <v>3</v>
+      </c>
     </row>
     <row r="23" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B23" s="1">
@@ -1818,7 +1825,7 @@
         <v>9</v>
       </c>
       <c r="G45" s="1">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="H45" s="1"/>
     </row>
@@ -1839,13 +1846,15 @@
       <c r="G46" s="1">
         <v>24</v>
       </c>
-      <c r="H46" s="1"/>
+      <c r="H46" s="1">
+        <v>23</v>
+      </c>
     </row>
     <row r="47" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B47" s="30">
+      <c r="B47" s="31">
         <v>42</v>
       </c>
-      <c r="C47" s="27" t="s">
+      <c r="C47" s="28" t="s">
         <v>82</v>
       </c>
       <c r="D47" s="3" t="s">
@@ -1863,8 +1872,8 @@
       <c r="H47" s="1"/>
     </row>
     <row r="48" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B48" s="31"/>
-      <c r="C48" s="28"/>
+      <c r="B48" s="32"/>
+      <c r="C48" s="29"/>
       <c r="D48" s="3" t="s">
         <v>78</v>
       </c>
@@ -1880,8 +1889,8 @@
       <c r="H48" s="1"/>
     </row>
     <row r="49" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B49" s="31"/>
-      <c r="C49" s="28"/>
+      <c r="B49" s="32"/>
+      <c r="C49" s="29"/>
       <c r="D49" s="3" t="s">
         <v>79</v>
       </c>
@@ -1897,8 +1906,8 @@
       <c r="H49" s="1"/>
     </row>
     <row r="50" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B50" s="31"/>
-      <c r="C50" s="28"/>
+      <c r="B50" s="32"/>
+      <c r="C50" s="29"/>
       <c r="D50" s="3" t="s">
         <v>76</v>
       </c>
@@ -1914,8 +1923,8 @@
       <c r="H50" s="1"/>
     </row>
     <row r="51" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B51" s="31"/>
-      <c r="C51" s="28"/>
+      <c r="B51" s="32"/>
+      <c r="C51" s="29"/>
       <c r="D51" s="3" t="s">
         <v>80</v>
       </c>
@@ -1931,8 +1940,8 @@
       <c r="H51" s="1"/>
     </row>
     <row r="52" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B52" s="32"/>
-      <c r="C52" s="29"/>
+      <c r="B52" s="33"/>
+      <c r="C52" s="30"/>
       <c r="D52" s="3" t="s">
         <v>81</v>
       </c>
@@ -1948,10 +1957,10 @@
       <c r="H52" s="1"/>
     </row>
     <row r="53" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B53" s="30">
+      <c r="B53" s="31">
         <v>43</v>
       </c>
-      <c r="C53" s="27" t="s">
+      <c r="C53" s="28" t="s">
         <v>83</v>
       </c>
       <c r="D53" s="3" t="s">
@@ -1969,8 +1978,8 @@
       <c r="H53" s="1"/>
     </row>
     <row r="54" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B54" s="31"/>
-      <c r="C54" s="28"/>
+      <c r="B54" s="32"/>
+      <c r="C54" s="29"/>
       <c r="D54" s="3" t="s">
         <v>85</v>
       </c>
@@ -1986,8 +1995,8 @@
       <c r="H54" s="1"/>
     </row>
     <row r="55" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B55" s="31"/>
-      <c r="C55" s="28"/>
+      <c r="B55" s="32"/>
+      <c r="C55" s="29"/>
       <c r="D55" s="3" t="s">
         <v>86</v>
       </c>
@@ -2003,8 +2012,8 @@
       <c r="H55" s="1"/>
     </row>
     <row r="56" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B56" s="31"/>
-      <c r="C56" s="28"/>
+      <c r="B56" s="32"/>
+      <c r="C56" s="29"/>
       <c r="D56" s="3" t="s">
         <v>87</v>
       </c>
@@ -2020,8 +2029,8 @@
       <c r="H56" s="1"/>
     </row>
     <row r="57" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B57" s="31"/>
-      <c r="C57" s="28"/>
+      <c r="B57" s="32"/>
+      <c r="C57" s="29"/>
       <c r="D57" s="3" t="s">
         <v>88</v>
       </c>
@@ -2037,8 +2046,8 @@
       <c r="H57" s="1"/>
     </row>
     <row r="58" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B58" s="31"/>
-      <c r="C58" s="28"/>
+      <c r="B58" s="32"/>
+      <c r="C58" s="29"/>
       <c r="D58" s="3" t="s">
         <v>89</v>
       </c>
@@ -2111,10 +2120,10 @@
       <c r="H61" s="1"/>
     </row>
     <row r="62" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B62" s="30">
+      <c r="B62" s="31">
         <v>47</v>
       </c>
-      <c r="C62" s="27" t="s">
+      <c r="C62" s="28" t="s">
         <v>111</v>
       </c>
       <c r="D62" s="3" t="s">
@@ -2132,8 +2141,8 @@
       <c r="H62" s="1"/>
     </row>
     <row r="63" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B63" s="31"/>
-      <c r="C63" s="28"/>
+      <c r="B63" s="32"/>
+      <c r="C63" s="29"/>
       <c r="D63" s="3" t="s">
         <v>117</v>
       </c>
@@ -2149,8 +2158,8 @@
       <c r="H63" s="1"/>
     </row>
     <row r="64" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B64" s="32"/>
-      <c r="C64" s="29"/>
+      <c r="B64" s="33"/>
+      <c r="C64" s="30"/>
       <c r="D64" s="3" t="s">
         <v>52</v>
       </c>
@@ -2187,10 +2196,10 @@
       <c r="H65" s="1"/>
     </row>
     <row r="66" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B66" s="26">
+      <c r="B66" s="27">
         <v>49</v>
       </c>
-      <c r="C66" s="36" t="s">
+      <c r="C66" s="37" t="s">
         <v>42</v>
       </c>
       <c r="D66" s="3" t="s">
@@ -2208,8 +2217,8 @@
       <c r="H66" s="1"/>
     </row>
     <row r="67" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B67" s="26"/>
-      <c r="C67" s="36"/>
+      <c r="B67" s="27"/>
+      <c r="C67" s="37"/>
       <c r="D67" s="3" t="s">
         <v>44</v>
       </c>
@@ -2225,8 +2234,8 @@
       <c r="H67" s="1"/>
     </row>
     <row r="68" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B68" s="26"/>
-      <c r="C68" s="36"/>
+      <c r="B68" s="27"/>
+      <c r="C68" s="37"/>
       <c r="D68" s="3" t="s">
         <v>46</v>
       </c>
@@ -2242,8 +2251,8 @@
       <c r="H68" s="1"/>
     </row>
     <row r="69" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B69" s="26"/>
-      <c r="C69" s="36"/>
+      <c r="B69" s="27"/>
+      <c r="C69" s="37"/>
       <c r="D69" s="3" t="s">
         <v>112</v>
       </c>
@@ -2259,8 +2268,8 @@
       <c r="H69" s="1"/>
     </row>
     <row r="70" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B70" s="26"/>
-      <c r="C70" s="36"/>
+      <c r="B70" s="27"/>
+      <c r="C70" s="37"/>
       <c r="D70" s="3" t="s">
         <v>45</v>
       </c>
@@ -2276,10 +2285,10 @@
       <c r="H70" s="1"/>
     </row>
     <row r="71" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B71" s="26">
+      <c r="B71" s="27">
         <v>50</v>
       </c>
-      <c r="C71" s="36" t="s">
+      <c r="C71" s="37" t="s">
         <v>47</v>
       </c>
       <c r="D71" s="3" t="s">
@@ -2297,8 +2306,8 @@
       <c r="H71" s="1"/>
     </row>
     <row r="72" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B72" s="26"/>
-      <c r="C72" s="36"/>
+      <c r="B72" s="27"/>
+      <c r="C72" s="37"/>
       <c r="D72" s="3" t="s">
         <v>49</v>
       </c>
@@ -2314,8 +2323,8 @@
       <c r="H72" s="1"/>
     </row>
     <row r="73" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B73" s="26"/>
-      <c r="C73" s="36"/>
+      <c r="B73" s="27"/>
+      <c r="C73" s="37"/>
       <c r="D73" s="3" t="s">
         <v>90</v>
       </c>
@@ -2331,8 +2340,8 @@
       <c r="H73" s="1"/>
     </row>
     <row r="74" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B74" s="26"/>
-      <c r="C74" s="36"/>
+      <c r="B74" s="27"/>
+      <c r="C74" s="37"/>
       <c r="D74" s="3" t="s">
         <v>114</v>
       </c>
@@ -2348,8 +2357,8 @@
       <c r="H74" s="1"/>
     </row>
     <row r="75" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B75" s="26"/>
-      <c r="C75" s="36"/>
+      <c r="B75" s="27"/>
+      <c r="C75" s="37"/>
       <c r="D75" s="3" t="s">
         <v>115</v>
       </c>
@@ -2365,10 +2374,10 @@
       <c r="H75" s="1"/>
     </row>
     <row r="76" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B76" s="30">
+      <c r="B76" s="31">
         <v>51</v>
       </c>
-      <c r="C76" s="27" t="s">
+      <c r="C76" s="28" t="s">
         <v>50</v>
       </c>
       <c r="D76" s="3" t="s">
@@ -2386,8 +2395,8 @@
       <c r="H76" s="1"/>
     </row>
     <row r="77" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B77" s="31"/>
-      <c r="C77" s="28"/>
+      <c r="B77" s="32"/>
+      <c r="C77" s="29"/>
       <c r="D77" s="3" t="s">
         <v>52</v>
       </c>
@@ -2403,8 +2412,8 @@
       <c r="H77" s="1"/>
     </row>
     <row r="78" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B78" s="32"/>
-      <c r="C78" s="29"/>
+      <c r="B78" s="33"/>
+      <c r="C78" s="30"/>
       <c r="D78" s="3" t="s">
         <v>112</v>
       </c>
@@ -2420,10 +2429,10 @@
       <c r="H78" s="1"/>
     </row>
     <row r="79" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B79" s="30">
+      <c r="B79" s="31">
         <v>52</v>
       </c>
-      <c r="C79" s="27" t="s">
+      <c r="C79" s="28" t="s">
         <v>53</v>
       </c>
       <c r="D79" s="3" t="s">
@@ -2441,8 +2450,8 @@
       <c r="H79" s="1"/>
     </row>
     <row r="80" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B80" s="31"/>
-      <c r="C80" s="28"/>
+      <c r="B80" s="32"/>
+      <c r="C80" s="29"/>
       <c r="D80" s="3" t="s">
         <v>51</v>
       </c>
@@ -2458,8 +2467,8 @@
       <c r="H80" s="1"/>
     </row>
     <row r="81" spans="1:43" x14ac:dyDescent="0.25">
-      <c r="B81" s="31"/>
-      <c r="C81" s="28"/>
+      <c r="B81" s="32"/>
+      <c r="C81" s="29"/>
       <c r="D81" s="3" t="s">
         <v>122</v>
       </c>
@@ -2475,8 +2484,8 @@
       <c r="H81" s="1"/>
     </row>
     <row r="82" spans="1:43" x14ac:dyDescent="0.25">
-      <c r="B82" s="31"/>
-      <c r="C82" s="28"/>
+      <c r="B82" s="32"/>
+      <c r="C82" s="29"/>
       <c r="D82" s="3" t="s">
         <v>55</v>
       </c>

--- a/Baba Balance material list_24_04_2026.xlsx
+++ b/Baba Balance material list_24_04_2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Amalgam_Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CB668635-F76C-4862-A367-A327247922C9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8D0DF41A-4ADF-4776-BF8C-BB021BCC0BD9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="243" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2775,7 +2775,9 @@
       <c r="G95" s="1">
         <v>232</v>
       </c>
-      <c r="H95" s="1"/>
+      <c r="H95" s="1">
+        <v>222</v>
+      </c>
     </row>
     <row r="96" spans="1:43" x14ac:dyDescent="0.25">
       <c r="B96" s="1">

--- a/Baba Balance material list_24_04_2026.xlsx
+++ b/Baba Balance material list_24_04_2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Amalgam_Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8D0DF41A-4ADF-4776-BF8C-BB021BCC0BD9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8CB3D2D7-0F9C-4454-A8D3-7D846E394059}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="243" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/Baba Balance material list_24_04_2026.xlsx
+++ b/Baba Balance material list_24_04_2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Amalgam_Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8CB3D2D7-0F9C-4454-A8D3-7D846E394059}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0E6FDFDC-2B2C-4F55-90B6-075AB8F1C376}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="243" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2759,7 +2759,7 @@
         <v>922</v>
       </c>
       <c r="H94" s="1">
-        <v>917</v>
+        <v>897</v>
       </c>
     </row>
     <row r="95" spans="1:43" x14ac:dyDescent="0.25">
@@ -2792,7 +2792,9 @@
       <c r="G96" s="1">
         <v>2000</v>
       </c>
-      <c r="H96" s="1"/>
+      <c r="H96" s="1">
+        <v>1950</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="15">
